--- a/artfynd/A 24540-2023 artfynd.xlsx
+++ b/artfynd/A 24540-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24540-2023 artfynd.xlsx
+++ b/artfynd/A 24540-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1806,6 +1806,103 @@
           <t>Steget Före</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126021871</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Flaskmyrbacken, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>631249</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6969908</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Högsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24540-2023 artfynd.xlsx
+++ b/artfynd/A 24540-2023 artfynd.xlsx
@@ -1812,7 +1812,7 @@
         <v>126021871</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 24540-2023 artfynd.xlsx
+++ b/artfynd/A 24540-2023 artfynd.xlsx
@@ -1812,7 +1812,7 @@
         <v>126021871</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 24540-2023 artfynd.xlsx
+++ b/artfynd/A 24540-2023 artfynd.xlsx
@@ -1812,7 +1812,7 @@
         <v>126021871</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 24540-2023 artfynd.xlsx
+++ b/artfynd/A 24540-2023 artfynd.xlsx
@@ -1812,7 +1812,7 @@
         <v>126021871</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 24540-2023 artfynd.xlsx
+++ b/artfynd/A 24540-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/159447</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/159448</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/159449</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/159450</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/159462</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/159463</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/246264</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1559,6 +1599,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/204620</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1670,6 +1715,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128983674</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1776,6 +1826,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/405187</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1887,6 +1942,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1599619</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1998,6 +2058,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1860611</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2109,6 +2174,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1860614</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2206,6 +2276,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126021871</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2317,6 +2392,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1896056</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2428,8 +2508,31 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1896059</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>